--- a/Results/Methanol/methanol climate change remind breakdown results.xlsx
+++ b/Results/Methanol/methanol climate change remind breakdown results.xlsx
@@ -521,34 +521,34 @@
         <v>0.8176128736045802</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2672282289984566</v>
+        <v>0.2672282289984568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4882558070015926</v>
+        <v>0.4882558070015925</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03017318194979636</v>
+        <v>0.03017318194979631</v>
       </c>
       <c r="H2" t="n">
-        <v>7.508784496133229e-05</v>
+        <v>7.508784496133217e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001186532738769451</v>
+        <v>0.0001186532738769452</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003943937727512737</v>
+        <v>0.0003943937727512739</v>
       </c>
       <c r="K2" t="n">
         <v>0.000379346935229613</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003479127878982789</v>
+        <v>0.0003479127878982793</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000334201316254814</v>
+        <v>0.0003342013162548133</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001200060968002246</v>
+        <v>0.001200060968002244</v>
       </c>
       <c r="O2" t="n">
         <v>0.02910599875576014</v>
@@ -569,40 +569,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.805176569397134</v>
+        <v>0.8051765693971341</v>
       </c>
       <c r="E3" t="n">
         <v>0.2671474298486587</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4865842964653776</v>
+        <v>0.4865842964653778</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01979926382768724</v>
+        <v>0.01979926382768728</v>
       </c>
       <c r="H3" t="n">
-        <v>5.953267764265676e-05</v>
+        <v>5.953267764265693e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.720893079672524e-05</v>
+        <v>9.720893079672531e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003309100714395545</v>
+        <v>0.0003309100714395542</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003664982901017474</v>
+        <v>0.0003664982901017471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003031302577692613</v>
+        <v>0.0003031302577696438</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000321511647124963</v>
+        <v>0.0003215116471249632</v>
       </c>
       <c r="N3" t="n">
         <v>0.00106078872015114</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910599866038432</v>
+        <v>0.02910599866038377</v>
       </c>
     </row>
     <row r="4">
@@ -620,40 +620,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7999564134561895</v>
+        <v>0.7999564134561892</v>
       </c>
       <c r="E4" t="n">
         <v>0.2698817205296968</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4861149770555101</v>
+        <v>0.4861149770555099</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01250230121302784</v>
+        <v>0.01250230121302781</v>
       </c>
       <c r="H4" t="n">
-        <v>4.879129851870849e-05</v>
+        <v>4.879129851870845e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>8.242078503874305e-05</v>
+        <v>8.2420785038743e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002873797842738779</v>
+        <v>0.0002873797842738762</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003594026147415707</v>
+        <v>0.0003594026147415705</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002700963798406237</v>
+        <v>0.0002700963798406353</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003109178953228116</v>
+        <v>0.0003109178953228118</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009924072266302424</v>
+        <v>0.0009924072266302433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02910599867358832</v>
+        <v>0.0291059986735881</v>
       </c>
     </row>
     <row r="5">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.789830784701549</v>
+        <v>0.7898307847015491</v>
       </c>
       <c r="E5" t="n">
         <v>0.2555559913989692</v>
@@ -680,31 +680,31 @@
         <v>0.483810033795798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01890331236210104</v>
+        <v>0.01890331236210102</v>
       </c>
       <c r="H5" t="n">
-        <v>5.635922067830315e-05</v>
+        <v>5.63592206783033e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.415883481072935e-05</v>
+        <v>9.415883481072942e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003182603305252028</v>
+        <v>0.0003182603305252018</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003619665949002916</v>
+        <v>0.0003619665949002915</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000294750683382097</v>
+        <v>0.0002947506833820981</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003144869833526036</v>
+        <v>0.0003144869833526041</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001015466185958883</v>
+        <v>0.001015466185958884</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599831107274</v>
+        <v>0.02910599831107286</v>
       </c>
     </row>
     <row r="6">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7614708455921423</v>
+        <v>0.7614708455921422</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2465306436778228</v>
+        <v>0.2465306436778226</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4799903697824478</v>
+        <v>0.4799903697824477</v>
       </c>
       <c r="G6" t="n">
         <v>0.003921842988284891</v>
       </c>
       <c r="H6" t="n">
-        <v>3.269832815897763e-05</v>
+        <v>3.269832815897764e-05</v>
       </c>
       <c r="I6" t="n">
         <v>6.357707388553073e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002203659522448973</v>
+        <v>0.0002203659522448961</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003309054335166837</v>
+        <v>0.0003309054335166834</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002272195912850235</v>
+        <v>0.0002272195912850219</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002904568291955262</v>
+        <v>0.0002904568291955275</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007567680393695158</v>
+        <v>0.0007567680393695167</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0291059978959306</v>
+        <v>0.02910599789593082</v>
       </c>
     </row>
     <row r="7">
@@ -773,40 +773,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7541786221933995</v>
+        <v>0.7541786221934</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2429012221933688</v>
+        <v>0.2429012221933689</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4789178129161027</v>
+        <v>0.4789178129161029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001578342388446852</v>
+        <v>0.001578342388446875</v>
       </c>
       <c r="H7" t="n">
-        <v>2.583501139415581e-05</v>
+        <v>2.58350113941555e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.703150177115064e-05</v>
+        <v>5.703150177115056e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001875225437057086</v>
+        <v>0.0001875225437057094</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003066585515984838</v>
+        <v>0.0003066585515984842</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002063021768262528</v>
+        <v>0.0002063021768271012</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002788087865749768</v>
+        <v>0.0002788087865749778</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006130883585121104</v>
+        <v>0.0006130883585121079</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910599776509826</v>
+        <v>0.02910599776509781</v>
       </c>
     </row>
     <row r="8">
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7624911818742218</v>
+        <v>0.7624911818742238</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2415314900677168</v>
+        <v>0.2415314900677167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4806886961775721</v>
+        <v>0.4806886961775709</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009033023779849152</v>
+        <v>0.009033023779849148</v>
       </c>
       <c r="H8" t="n">
-        <v>4.126272957781061e-05</v>
+        <v>4.126272957781063e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.265592233550225e-05</v>
+        <v>7.265592233550222e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002546547806893589</v>
+        <v>0.0002546547806893609</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003433430119693657</v>
+        <v>0.000343343011969366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002526229778490397</v>
+        <v>0.0002526229778494624</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002992408204281959</v>
+        <v>0.0002992408204281956</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008681938368657683</v>
+        <v>0.0008681938368657692</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910599776936873</v>
+        <v>0.02910599776937151</v>
       </c>
     </row>
     <row r="9">
@@ -878,37 +878,37 @@
         <v>0.7232344761044154</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2178732829826222</v>
+        <v>0.2178732829826221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4734956181293405</v>
+        <v>0.4734956181293406</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00106542215718156</v>
+        <v>0.001065422157181512</v>
       </c>
       <c r="H9" t="n">
-        <v>2.563357951726059e-05</v>
+        <v>2.563357951726015e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>5.640768438450202e-05</v>
+        <v>5.6407684384502e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001878255594395182</v>
+        <v>0.0001878255594395179</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003095530133562662</v>
+        <v>0.0003095530133562656</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002059496929954642</v>
+        <v>0.0002059496929954471</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0002792912927835891</v>
+        <v>0.0002792912927835886</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0006294949974389393</v>
+        <v>0.0006294949974389356</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599701535554</v>
+        <v>0.02910599701535566</v>
       </c>
     </row>
     <row r="10">
@@ -926,40 +926,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7090213199991668</v>
+        <v>0.7090213199991662</v>
       </c>
       <c r="E10" t="n">
         <v>0.2157640979134274</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4621111202396366</v>
+        <v>0.4621111202396367</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0006310792245726919</v>
+        <v>0.0006310792245726907</v>
       </c>
       <c r="H10" t="n">
-        <v>1.941576900401819e-05</v>
+        <v>1.941576900401797e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>5.17088141036886e-05</v>
+        <v>5.170881410368868e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001571588557477472</v>
+        <v>0.0001571588557477467</v>
       </c>
       <c r="K10" t="n">
         <v>0.0002818120950957679</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001878502249654523</v>
+        <v>0.0001878502249644482</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002604720881249717</v>
+        <v>0.0002604720881249709</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0004506075567126564</v>
+        <v>0.0004506075567126557</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910599721777574</v>
+        <v>0.02910599721777607</v>
       </c>
     </row>
   </sheetData>
@@ -1066,37 +1066,37 @@
         <v>0.5153058104885051</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2672282289984566</v>
+        <v>0.2672282289984568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1859487363971418</v>
+        <v>0.1859487363971419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03017318194979636</v>
+        <v>0.03017318194979631</v>
       </c>
       <c r="H2" t="n">
-        <v>7.508784496133229e-05</v>
+        <v>7.508784496133217e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001186532738769451</v>
+        <v>0.0001186532738769452</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003943937727512737</v>
+        <v>0.0003943937727512739</v>
       </c>
       <c r="K2" t="n">
         <v>0.000379346935229613</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003479127878982789</v>
+        <v>0.0003479127878982793</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000334201316254814</v>
+        <v>0.0003342013162548133</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001200060968002246</v>
+        <v>0.001200060968002244</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600624413578</v>
+        <v>0.02910600624413567</v>
       </c>
     </row>
     <row r="3">
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4834208114528938</v>
+        <v>0.4834208114528942</v>
       </c>
       <c r="E3" t="n">
         <v>0.2671474298486587</v>
       </c>
       <c r="F3" t="n">
-        <v>0.164828530551001</v>
+        <v>0.1648285305510012</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01979926382768724</v>
+        <v>0.01979926382768728</v>
       </c>
       <c r="H3" t="n">
-        <v>5.953267764265676e-05</v>
+        <v>5.953267764265693e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.720893079672524e-05</v>
+        <v>9.720893079672531e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003309100714395545</v>
+        <v>0.0003309100714395542</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003664982901017474</v>
+        <v>0.0003664982901017471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003031302577692613</v>
+        <v>0.0003031302577696438</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000321511647124963</v>
+        <v>0.0003215116471249632</v>
       </c>
       <c r="N3" t="n">
         <v>0.00106078872015114</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600663052071</v>
+        <v>0.02910600663052049</v>
       </c>
     </row>
     <row r="4">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4646724527004891</v>
+        <v>0.4646724527004893</v>
       </c>
       <c r="E4" t="n">
         <v>0.2698817205296968</v>
@@ -1174,31 +1174,31 @@
         <v>0.1508310079945716</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01250230121302784</v>
+        <v>0.01250230121302781</v>
       </c>
       <c r="H4" t="n">
-        <v>4.879129851870849e-05</v>
+        <v>4.879129851870845e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>8.242078503874305e-05</v>
+        <v>8.2420785038743e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002873797842738779</v>
+        <v>0.0002873797842738762</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003594026147415707</v>
+        <v>0.0003594026147415705</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002700963798406237</v>
+        <v>0.0002700963798406353</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003109178953228116</v>
+        <v>0.0003109178953228118</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0009924072266302424</v>
+        <v>0.0009924072266302433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0291060069788262</v>
+        <v>0.02910600697882648</v>
       </c>
     </row>
     <row r="5">
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4654479939243051</v>
+        <v>0.4654479939243053</v>
       </c>
       <c r="E5" t="n">
         <v>0.2555559913989692</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1594272349833452</v>
+        <v>0.1594272349833451</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01890331236210104</v>
+        <v>0.01890331236210102</v>
       </c>
       <c r="H5" t="n">
-        <v>5.635922067830315e-05</v>
+        <v>5.63592206783033e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.415883481072935e-05</v>
+        <v>9.415883481072942e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003182603305252028</v>
+        <v>0.0003182603305252018</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003619665949002916</v>
+        <v>0.0003619665949002915</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000294750683382097</v>
+        <v>0.0002947506833820981</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003144869833526036</v>
+        <v>0.0003144869833526041</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001015466185958883</v>
+        <v>0.001015466185958884</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910600634628152</v>
+        <v>0.0291060063462818</v>
       </c>
     </row>
     <row r="6">
@@ -1267,40 +1267,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4076584096938254</v>
+        <v>0.4076584096938252</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2465306436778228</v>
+        <v>0.2465306436778226</v>
       </c>
       <c r="F6" t="n">
-        <v>0.126177925119927</v>
+        <v>0.1261779251199269</v>
       </c>
       <c r="G6" t="n">
         <v>0.003921842988284891</v>
       </c>
       <c r="H6" t="n">
-        <v>3.269832815897763e-05</v>
+        <v>3.269832815897764e-05</v>
       </c>
       <c r="I6" t="n">
         <v>6.357707388553073e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002203659522448973</v>
+        <v>0.0002203659522448961</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003309054335166837</v>
+        <v>0.0003309054335166834</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002272195912850235</v>
+        <v>0.0002272195912850219</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002904568291955262</v>
+        <v>0.0002904568291955275</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007567680393695158</v>
+        <v>0.0007567680393695167</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600666013458</v>
+        <v>0.02910600666013463</v>
       </c>
     </row>
     <row r="7">
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3955308079157694</v>
+        <v>0.3955308079157695</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2429012221933688</v>
+        <v>0.2429012221933689</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202699897544924</v>
+        <v>0.1202699897544925</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001578342388446852</v>
+        <v>0.001578342388446875</v>
       </c>
       <c r="H7" t="n">
-        <v>2.583501139415581e-05</v>
+        <v>2.58350113941555e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.703150177115064e-05</v>
+        <v>5.703150177115056e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001875225437057086</v>
+        <v>0.0001875225437057094</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003066585515984838</v>
+        <v>0.0003066585515984842</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002063021768262528</v>
+        <v>0.0002063021768271012</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002788087865749768</v>
+        <v>0.0002788087865749778</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006130883585121104</v>
+        <v>0.0006130883585121079</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600664907848</v>
+        <v>0.02910600664907753</v>
       </c>
     </row>
     <row r="8">
@@ -1372,37 +1372,37 @@
         <v>0.4168387202451334</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2415314900677168</v>
+        <v>0.2415314900677167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.135036225986409</v>
+        <v>0.1350362259864091</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009033023779849152</v>
+        <v>0.009033023779849148</v>
       </c>
       <c r="H8" t="n">
-        <v>4.126272957781061e-05</v>
+        <v>4.126272957781063e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.265592233550225e-05</v>
+        <v>7.265592233550222e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002546547806893589</v>
+        <v>0.0002546547806893609</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003433430119693657</v>
+        <v>0.000343343011969366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002526229778490397</v>
+        <v>0.0002526229778494624</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002992408204281959</v>
+        <v>0.0002992408204281956</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008681938368657683</v>
+        <v>0.0008681938368657692</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910600633144333</v>
+        <v>0.029106006331443</v>
       </c>
     </row>
     <row r="9">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3612501119575774</v>
+        <v>0.3612501119575768</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2178732829826222</v>
+        <v>0.2178732829826221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.111511245015873</v>
+        <v>0.1115112450158727</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00106542215718156</v>
+        <v>0.001065422157181512</v>
       </c>
       <c r="H9" t="n">
-        <v>2.563357951726059e-05</v>
+        <v>2.563357951726015e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>5.640768438450202e-05</v>
+        <v>5.6407684384502e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001878255594395182</v>
+        <v>0.0001878255594395179</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003095530133562662</v>
+        <v>0.0003095530133562656</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002059496929954642</v>
+        <v>0.0002059496929954471</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0002792912927835891</v>
+        <v>0.0002792912927835886</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0006294949974389393</v>
+        <v>0.0006294949974389356</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600598198504</v>
+        <v>0.02910600598198498</v>
       </c>
     </row>
     <row r="10">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.356851108682442</v>
+        <v>0.3568511086824415</v>
       </c>
       <c r="E10" t="n">
         <v>0.2157640979134274</v>
@@ -1480,31 +1480,31 @@
         <v>0.1099409001993871</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0006310792245726919</v>
+        <v>0.0006310792245726907</v>
       </c>
       <c r="H10" t="n">
-        <v>1.941576900401819e-05</v>
+        <v>1.941576900401797e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>5.17088141036886e-05</v>
+        <v>5.170881410368868e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001571588557477472</v>
+        <v>0.0001571588557477467</v>
       </c>
       <c r="K10" t="n">
         <v>0.0002818120950957679</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001878502249654523</v>
+        <v>0.0001878502249644482</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002604720881249717</v>
+        <v>0.0002604720881249709</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0004506075567126564</v>
+        <v>0.0004506075567126557</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910600594130058</v>
+        <v>0.02910600594130097</v>
       </c>
     </row>
   </sheetData>
@@ -1663,67 +1663,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.019141429889647</v>
+        <v>-1.019141429889652</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.559063565100554</v>
+        <v>-1.559063565100552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2854433532441241</v>
+        <v>0.2854433532441244</v>
       </c>
       <c r="G2" t="n">
-        <v>2.761669111764114e-07</v>
+        <v>2.761669111764112e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.583610202153019e-06</v>
+        <v>7.583610202153034e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.262056182651839e-05</v>
+        <v>9.262056182651773e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00034115986546792</v>
+        <v>0.0003411598654679199</v>
       </c>
       <c r="K2" t="n">
-        <v>2.006979350325122e-05</v>
+        <v>2.006979350318942e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.017943967169646e-05</v>
+        <v>1.017943967169584e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.941187226744917e-05</v>
+        <v>4.94118722674492e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006302451847923555</v>
+        <v>0.00630245184793262</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002426031438041061</v>
+        <v>0.002426031438041062</v>
       </c>
       <c r="P2" t="n">
-        <v>3.091245712846874e-05</v>
+        <v>3.091245712846872e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02986595231014755</v>
+        <v>0.02986595231012155</v>
       </c>
       <c r="R2" t="n">
         <v>0.0001628288364327003</v>
       </c>
       <c r="S2" t="n">
-        <v>5.169039934467401e-06</v>
+        <v>5.169039934467407e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1350987264549081</v>
+        <v>0.1350987264549083</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03547067614020506</v>
+        <v>0.0354706761402051</v>
       </c>
       <c r="V2" t="n">
         <v>2.991450848324466e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003809876879135909</v>
+        <v>0.0003809876879135905</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01386906203123722</v>
+        <v>0.01386906203123719</v>
       </c>
       <c r="Y2" t="n">
         <v>0.0303416526368951</v>
@@ -1747,67 +1747,67 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.12420563135357</v>
+        <v>-1.124205631353592</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.567329179523423</v>
+        <v>-1.567329179523424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2515327988334877</v>
+        <v>0.2515327988334882</v>
       </c>
       <c r="G3" t="n">
-        <v>2.692495566807694e-07</v>
+        <v>2.692495566807682e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>7.289007861914825e-06</v>
+        <v>7.289007861914838e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.771186780404287e-05</v>
+        <v>7.771186780404286e-05</v>
       </c>
       <c r="J3" t="n">
         <v>0.0002922211285163694</v>
       </c>
       <c r="K3" t="n">
-        <v>1.515026899451322e-05</v>
+        <v>1.51502689945132e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.82484184570812e-06</v>
+        <v>7.824841845708134e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.000381873355771e-05</v>
+        <v>4.000381873355774e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004761391042062428</v>
+        <v>0.004761391042061684</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001579801963900485</v>
+        <v>0.001579801963900486</v>
       </c>
       <c r="P3" t="n">
-        <v>2.539884965996651e-05</v>
+        <v>2.539884965996654e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02278372254079912</v>
+        <v>0.02278372254080168</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001209232842262594</v>
+        <v>0.0001209232842262595</v>
       </c>
       <c r="S3" t="n">
-        <v>4.644714719611901e-06</v>
+        <v>4.644714719611884e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08896275042748446</v>
+        <v>0.08896275042748486</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03156397257714588</v>
+        <v>0.03156397257714592</v>
       </c>
       <c r="V3" t="n">
-        <v>2.772245865079849e-06</v>
+        <v>2.77224586507985e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003588791288868767</v>
+        <v>0.0003588791288868769</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01298307465424495</v>
+        <v>0.01298307465424493</v>
       </c>
       <c r="Y3" t="n">
         <v>0.02800291181003578</v>
@@ -1831,70 +1831,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.189978097183264</v>
+        <v>-1.1899780971833</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.573219727399015</v>
+        <v>-1.573219727399013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2360399299638538</v>
+        <v>0.236039929963854</v>
       </c>
       <c r="G4" t="n">
-        <v>2.648164763026867e-07</v>
+        <v>2.648164763026866e-07</v>
       </c>
       <c r="H4" t="n">
         <v>7.073304207949564e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>6.748909063991845e-05</v>
+        <v>6.748909063991802e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002624910296197445</v>
+        <v>0.0002624910296197435</v>
       </c>
       <c r="K4" t="n">
-        <v>1.200007627855245e-05</v>
+        <v>1.200007627857962e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.828183141919372e-06</v>
+        <v>5.828183141979014e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.502950038710189e-05</v>
+        <v>3.502950038710193e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003567598529931513</v>
+        <v>0.003567598529931511</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001112333318218446</v>
+        <v>0.001112333318218445</v>
       </c>
       <c r="P4" t="n">
-        <v>2.249750005340636e-05</v>
+        <v>2.249750005340634e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01777924469770814</v>
+        <v>0.01777924469769828</v>
       </c>
       <c r="R4" t="n">
-        <v>9.599275579775138e-05</v>
+        <v>9.599275579775146e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.232420971918226e-06</v>
+        <v>4.232420971918214e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05651169876996132</v>
+        <v>0.05651169876996144</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02877680311982534</v>
+        <v>0.02877680311982532</v>
       </c>
       <c r="V4" t="n">
-        <v>2.62923873965701e-06</v>
+        <v>2.629238739657008e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003415158359136895</v>
+        <v>0.0003415158359136905</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01229729657868706</v>
+        <v>0.01229729657868709</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02629964727778474</v>
+        <v>0.02629964727778472</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1915,70 +1915,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.147901547339879</v>
+        <v>-1.14790154733987</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.58828161444517</v>
+        <v>-1.588281614445171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2553969155297907</v>
+        <v>0.2553969155297909</v>
       </c>
       <c r="G5" t="n">
-        <v>2.665204581106074e-07</v>
+        <v>2.665204581106058e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.163468546203941e-06</v>
+        <v>7.16346854620395e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>7.47411664608802e-05</v>
+        <v>7.474116646088053e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000280658818757847</v>
+        <v>0.0002806588187578473</v>
       </c>
       <c r="K5" t="n">
-        <v>1.285068047712325e-05</v>
+        <v>1.285068047712329e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.837409510672577e-06</v>
+        <v>3.837409510672719e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.775735238594354e-05</v>
+        <v>3.775735238594349e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004201264662515716</v>
+        <v>0.004201264662515718</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00193851420832335</v>
+        <v>0.001938514208323963</v>
       </c>
       <c r="P5" t="n">
-        <v>2.40976418135652e-05</v>
+        <v>2.409764181356524e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0220168986277072</v>
+        <v>0.02201689862766348</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001398131546923977</v>
+        <v>0.0001398131546922783</v>
       </c>
       <c r="S5" t="n">
-        <v>4.481883810626935e-06</v>
+        <v>4.48188381062693e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08497176690150431</v>
+        <v>0.08497176690150429</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03079146666181657</v>
+        <v>0.03079146666181661</v>
       </c>
       <c r="V5" t="n">
-        <v>2.648566676086906e-06</v>
+        <v>2.648566676086905e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003357775868105733</v>
+        <v>0.0003357775868105736</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01262194038716203</v>
+        <v>0.01262194038716204</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02751716983688131</v>
+        <v>0.02751716983688129</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1999,70 +1999,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.297360266472118</v>
+        <v>-1.297360266472128</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.600390566661065</v>
+        <v>-1.600390566661067</v>
       </c>
       <c r="F6" t="n">
         <v>0.2082320883459166</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5631610454578e-07</v>
+        <v>2.563161045457806e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>6.671573010948773e-06</v>
+        <v>6.671573010948768e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.17513706212342e-05</v>
+        <v>5.175137062123434e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002235525539094359</v>
+        <v>0.0002235525539087687</v>
       </c>
       <c r="K6" t="n">
-        <v>9.585839132261649e-06</v>
+        <v>9.585839132261671e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>2.90864822007827e-06</v>
+        <v>2.908648220078291e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9390491085105e-05</v>
+        <v>2.939049108510493e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003102937080028138</v>
+        <v>0.00310293708002811</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006213565869026629</v>
+        <v>0.0006213565869026663</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92485384672615e-05</v>
+        <v>1.924853846726155e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01146407561191111</v>
+        <v>0.01146407561192377</v>
       </c>
       <c r="R6" t="n">
-        <v>8.456409261616574e-05</v>
+        <v>8.45640926161655e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.677714219969843e-06</v>
+        <v>3.677714219969792e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01833026327061529</v>
+        <v>0.01833026327061504</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02533583789501209</v>
+        <v>0.02533583789501207</v>
       </c>
       <c r="V6" t="n">
-        <v>2.462720827515054e-06</v>
+        <v>2.462720827515053e-06</v>
       </c>
       <c r="W6" t="n">
         <v>0.0003160411495889312</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01156113660926162</v>
+        <v>0.01156113660926156</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02363246123643952</v>
+        <v>0.02363246123643949</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2083,70 +2083,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.341601046001076</v>
+        <v>-1.341601046001074</v>
       </c>
       <c r="E7" t="n">
         <v>-1.60627723273427</v>
       </c>
       <c r="F7" t="n">
-        <v>0.187595368385777</v>
+        <v>0.1875953683857767</v>
       </c>
       <c r="G7" t="n">
-        <v>2.504239571973477e-07</v>
+        <v>2.5042395719735e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.557525404993905e-06</v>
+        <v>6.55752540499393e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.403833060547296e-05</v>
+        <v>4.403833060547338e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001944709708000404</v>
+        <v>0.0001944709708000412</v>
       </c>
       <c r="K7" t="n">
-        <v>8.239289168073098e-06</v>
+        <v>8.239289168073076e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.522145043742541e-06</v>
+        <v>2.522145043742545e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>2.519678914462556e-05</v>
+        <v>2.519678914462561e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002664239381850308</v>
+        <v>0.00266423938183662</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0004912265164651931</v>
+        <v>0.0004912265164651954</v>
       </c>
       <c r="P7" t="n">
-        <v>1.660874059878223e-05</v>
+        <v>1.66087405987822e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009015912887515973</v>
+        <v>0.009015912887513515</v>
       </c>
       <c r="R7" t="n">
         <v>6.914641102902019e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.300454012836435e-06</v>
+        <v>3.300454012836477e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007875337957197599</v>
+        <v>0.007875337957198436</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02334079816885376</v>
+        <v>0.02334079816885375</v>
       </c>
       <c r="V7" t="n">
         <v>2.362744815371567e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003047171912796707</v>
+        <v>0.000304717191279671</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01093926732138754</v>
+        <v>0.01093926732138756</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0220765931127416</v>
+        <v>0.02207659311274162</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2167,58 +2167,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.23257461334495</v>
+        <v>-1.232574613344944</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.594531383761507</v>
+        <v>-1.594531383761506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.235030640121674</v>
+        <v>0.2350306401216745</v>
       </c>
       <c r="G8" t="n">
-        <v>2.60191542639818e-07</v>
+        <v>2.601915426398179e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.798745828676001e-06</v>
+        <v>6.798745828676002e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.980385718243052e-05</v>
+        <v>5.980385718243096e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002487977476780348</v>
+        <v>0.0002487977476780352</v>
       </c>
       <c r="K8" t="n">
-        <v>1.082933422012096e-05</v>
+        <v>1.082933422012095e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.155360374887882e-06</v>
+        <v>3.155360374885295e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.321850514948562e-05</v>
+        <v>3.321850514948567e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003426553061865885</v>
+        <v>0.003426553061873118</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001625892900298988</v>
+        <v>0.001625892900298989</v>
       </c>
       <c r="P8" t="n">
-        <v>2.152746894981349e-05</v>
+        <v>2.152746894981348e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01524758646021822</v>
+        <v>0.01524758646023521</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001229711754075643</v>
+        <v>0.0001229711754075651</v>
       </c>
       <c r="S8" t="n">
-        <v>4.009776762668648e-06</v>
+        <v>4.00977676266871e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04107363540280808</v>
+        <v>0.04107363540280843</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0274636078008333</v>
+        <v>0.02746360780083333</v>
       </c>
       <c r="V8" t="n">
         <v>2.541194588843778e-06</v>
@@ -2227,10 +2227,10 @@
         <v>0.0003252259760717383</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01201460822552784</v>
+        <v>0.01201460822552787</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02523507340505805</v>
+        <v>0.02523507340505812</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2251,70 +2251,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.342264262624156</v>
+        <v>-1.34226426262418</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.605792974238931</v>
+        <v>-1.605792974238932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1891278732299562</v>
+        <v>0.1891278732299564</v>
       </c>
       <c r="G9" t="n">
-        <v>2.504146146646007e-07</v>
+        <v>2.504146146645995e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>6.556318782835718e-06</v>
+        <v>6.556318782835706e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>4.410949168723157e-05</v>
+        <v>4.410949168723167e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001923390322356383</v>
+        <v>0.0001923390322356375</v>
       </c>
       <c r="K9" t="n">
-        <v>7.805243129140956e-06</v>
+        <v>7.805243129140942e-06</v>
       </c>
       <c r="L9" t="n">
         <v>2.488528586518843e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.462544083629329e-05</v>
+        <v>2.462544083629322e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002448999934092788</v>
+        <v>0.002448999934082491</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0004889631384711481</v>
+        <v>0.0004889631384708728</v>
       </c>
       <c r="P9" t="n">
-        <v>1.625369198364374e-05</v>
+        <v>1.625369198364369e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008731578610435678</v>
+        <v>0.008731578610453639</v>
       </c>
       <c r="R9" t="n">
-        <v>7.040323148520276e-05</v>
+        <v>7.040323148520267e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.314979553935994e-06</v>
+        <v>3.314979553935917e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005601689164160739</v>
+        <v>0.00560168916416057</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02335356750553526</v>
+        <v>0.02335356750553519</v>
       </c>
       <c r="V9" t="n">
-        <v>2.353440918845096e-06</v>
+        <v>2.353440918845094e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003056315554172025</v>
+        <v>0.000305631555417202</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01093500427019157</v>
+        <v>0.01093500427019158</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02216487253146286</v>
+        <v>0.02216487253146285</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2335,70 +2335,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.381333991894105</v>
+        <v>-1.381333991894089</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.612434062968964</v>
+        <v>-1.612434062968962</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1650890647286761</v>
+        <v>0.1650890647286752</v>
       </c>
       <c r="G10" t="n">
-        <v>2.437057436126674e-07</v>
+        <v>2.437057436126669e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>6.401146711956973e-06</v>
+        <v>6.401146711956965e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>3.690763526469011e-05</v>
+        <v>3.690763526468981e-05</v>
       </c>
       <c r="J10" t="n">
         <v>0.0001591744440864191</v>
       </c>
       <c r="K10" t="n">
-        <v>6.232301462574511e-06</v>
+        <v>6.232301462574491e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>2.038390667617894e-06</v>
+        <v>2.03839066761789e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>2.022753678463053e-05</v>
+        <v>2.02275367846304e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001997654717967101</v>
+        <v>0.001997654717969489</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0003962917553510036</v>
+        <v>0.0003962917553510028</v>
       </c>
       <c r="P10" t="n">
-        <v>1.33859808109951e-05</v>
+        <v>1.338598081099503e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.007125988120674628</v>
+        <v>0.007125988120684126</v>
       </c>
       <c r="R10" t="n">
-        <v>6.153988721056384e-05</v>
+        <v>6.153988721059192e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.896904983858844e-06</v>
+        <v>2.896904983858831e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0036227855866727</v>
+        <v>0.003622785586672703</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02145993041192557</v>
+        <v>0.02145993041192556</v>
       </c>
       <c r="V10" t="n">
         <v>2.238315205429518e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002926020834925043</v>
+        <v>0.0002926020834925045</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01020480014999298</v>
+        <v>0.010204800149993</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02059963552342418</v>
+        <v>0.02059963552342421</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2560,67 +2560,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.9031709771374339</v>
+        <v>-0.9031709771374251</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.559063565100554</v>
+        <v>-1.559063565100552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4014138060406492</v>
+        <v>0.4014138060406495</v>
       </c>
       <c r="G2" t="n">
-        <v>2.761669111764114e-07</v>
+        <v>2.761669111764112e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.583610202153019e-06</v>
+        <v>7.583610202153034e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.262056182651839e-05</v>
+        <v>9.262056182651773e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00034115986546792</v>
+        <v>0.0003411598654679199</v>
       </c>
       <c r="K2" t="n">
-        <v>2.006979350325122e-05</v>
+        <v>2.006979350318942e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.017943967169646e-05</v>
+        <v>1.017943967169584e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.941187226744917e-05</v>
+        <v>4.94118722674492e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006302451847923555</v>
+        <v>0.00630245184793262</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002426031438041061</v>
+        <v>0.002426031438041062</v>
       </c>
       <c r="P2" t="n">
-        <v>3.091245712846874e-05</v>
+        <v>3.091245712846872e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02986595231014755</v>
+        <v>0.02986595231012155</v>
       </c>
       <c r="R2" t="n">
         <v>0.0001628288364327003</v>
       </c>
       <c r="S2" t="n">
-        <v>5.169039934467401e-06</v>
+        <v>5.169039934467407e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1350987264549081</v>
+        <v>0.1350987264549083</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03547067614020506</v>
+        <v>0.0354706761402051</v>
       </c>
       <c r="V2" t="n">
         <v>2.991450848324466e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003809876879135909</v>
+        <v>0.0003809876879135905</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01386906203123722</v>
+        <v>0.01386906203123719</v>
       </c>
       <c r="Y2" t="n">
         <v>0.0303416526368951</v>
@@ -2644,67 +2644,67 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.051593715662002</v>
+        <v>-1.051593715662021</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.567329179523423</v>
+        <v>-1.567329179523424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3241447145528038</v>
+        <v>0.324144714552804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.692495566807694e-07</v>
+        <v>2.692495566807682e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>7.289007861914825e-06</v>
+        <v>7.289007861914838e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.771186780404287e-05</v>
+        <v>7.771186780404286e-05</v>
       </c>
       <c r="J3" t="n">
         <v>0.0002922211285163694</v>
       </c>
       <c r="K3" t="n">
-        <v>1.515026899451322e-05</v>
+        <v>1.51502689945132e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.82484184570812e-06</v>
+        <v>7.824841845708134e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.000381873355771e-05</v>
+        <v>4.000381873355774e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004761391042062428</v>
+        <v>0.004761391042061684</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001579801963900485</v>
+        <v>0.001579801963900486</v>
       </c>
       <c r="P3" t="n">
-        <v>2.539884965996651e-05</v>
+        <v>2.539884965996654e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02278372254079912</v>
+        <v>0.02278372254080168</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001209232842262594</v>
+        <v>0.0001209232842262595</v>
       </c>
       <c r="S3" t="n">
-        <v>4.644714719611901e-06</v>
+        <v>4.644714719611884e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08896275042748446</v>
+        <v>0.08896275042748486</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03156397257714588</v>
+        <v>0.03156397257714592</v>
       </c>
       <c r="V3" t="n">
-        <v>2.772245865079849e-06</v>
+        <v>2.77224586507985e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003588791288868767</v>
+        <v>0.0003588791288868769</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01298307465424495</v>
+        <v>0.01298307465424493</v>
       </c>
       <c r="Y3" t="n">
         <v>0.02800291181003578</v>
@@ -2728,70 +2728,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.14109757979315</v>
+        <v>-1.141097579793108</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.573219727399015</v>
+        <v>-1.573219727399013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2849204473726633</v>
+        <v>0.2849204473726631</v>
       </c>
       <c r="G4" t="n">
-        <v>2.648164763026867e-07</v>
+        <v>2.648164763026866e-07</v>
       </c>
       <c r="H4" t="n">
         <v>7.073304207949564e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>6.748909063991845e-05</v>
+        <v>6.748909063991802e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002624910296197445</v>
+        <v>0.0002624910296197435</v>
       </c>
       <c r="K4" t="n">
-        <v>1.200007627855245e-05</v>
+        <v>1.200007627857962e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.828183141919372e-06</v>
+        <v>5.828183141979014e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.502950038710189e-05</v>
+        <v>3.502950038710193e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003567598529931513</v>
+        <v>0.003567598529931511</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001112333318218446</v>
+        <v>0.001112333318218445</v>
       </c>
       <c r="P4" t="n">
-        <v>2.249750005340636e-05</v>
+        <v>2.249750005340634e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01777924469770814</v>
+        <v>0.01777924469769828</v>
       </c>
       <c r="R4" t="n">
-        <v>9.599275579775138e-05</v>
+        <v>9.599275579775146e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.232420971918226e-06</v>
+        <v>4.232420971918214e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05651169876996132</v>
+        <v>0.05651169876996144</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02877680311982534</v>
+        <v>0.02877680311982532</v>
       </c>
       <c r="V4" t="n">
-        <v>2.62923873965701e-06</v>
+        <v>2.629238739657008e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003415158359136895</v>
+        <v>0.0003415158359136905</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01229729657868706</v>
+        <v>0.01229729657868709</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02629964727778474</v>
+        <v>0.02629964727778472</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2812,70 +2812,70 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.055520381490153</v>
+        <v>-1.055520381490162</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.58828161444517</v>
+        <v>-1.588281614445171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3477780814148123</v>
+        <v>0.3477780814148119</v>
       </c>
       <c r="G5" t="n">
-        <v>2.665204581106074e-07</v>
+        <v>2.665204581106058e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.163468546203941e-06</v>
+        <v>7.16346854620395e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>7.47411664608802e-05</v>
+        <v>7.474116646088053e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000280658818757847</v>
+        <v>0.0002806588187578473</v>
       </c>
       <c r="K5" t="n">
-        <v>1.285068047712325e-05</v>
+        <v>1.285068047712329e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.837409510672577e-06</v>
+        <v>3.837409510672719e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.775735238594354e-05</v>
+        <v>3.775735238594349e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004201264662515716</v>
+        <v>0.004201264662515718</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00193851420832335</v>
+        <v>0.001938514208323963</v>
       </c>
       <c r="P5" t="n">
-        <v>2.40976418135652e-05</v>
+        <v>2.409764181356524e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0220168986277072</v>
+        <v>0.02201689862766348</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001398131546923977</v>
+        <v>0.0001398131546922783</v>
       </c>
       <c r="S5" t="n">
-        <v>4.481883810626935e-06</v>
+        <v>4.48188381062693e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08497176690150431</v>
+        <v>0.08497176690150429</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03079146666181657</v>
+        <v>0.03079146666181661</v>
       </c>
       <c r="V5" t="n">
-        <v>2.648566676086906e-06</v>
+        <v>2.648566676086905e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003357775868105733</v>
+        <v>0.0003357775868105736</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01262194038716203</v>
+        <v>0.01262194038716204</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02751716983688131</v>
+        <v>0.02751716983688129</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2896,70 +2896,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.242720704062577</v>
+        <v>-1.242720704062578</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.600390566661065</v>
+        <v>-1.600390566661067</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2628716507763377</v>
+        <v>0.2628716507763376</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5631610454578e-07</v>
+        <v>2.563161045457806e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>6.671573010948773e-06</v>
+        <v>6.671573010948768e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.17513706212342e-05</v>
+        <v>5.175137062123434e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002235525539094359</v>
+        <v>0.0002235525539087687</v>
       </c>
       <c r="K6" t="n">
-        <v>9.585839132261649e-06</v>
+        <v>9.585839132261671e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>2.90864822007827e-06</v>
+        <v>2.908648220078291e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9390491085105e-05</v>
+        <v>2.939049108510493e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003102937080028138</v>
+        <v>0.00310293708002811</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006213565869026629</v>
+        <v>0.0006213565869026663</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92485384672615e-05</v>
+        <v>1.924853846726155e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01146407561191111</v>
+        <v>0.01146407561192377</v>
       </c>
       <c r="R6" t="n">
-        <v>8.456409261616574e-05</v>
+        <v>8.45640926161655e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.677714219969843e-06</v>
+        <v>3.677714219969792e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01833026327061529</v>
+        <v>0.01833026327061504</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02533583789501209</v>
+        <v>0.02533583789501207</v>
       </c>
       <c r="V6" t="n">
-        <v>2.462720827515054e-06</v>
+        <v>2.462720827515053e-06</v>
       </c>
       <c r="W6" t="n">
         <v>0.0003160411495889312</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01156113660926162</v>
+        <v>0.01156113660926156</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02363246123643952</v>
+        <v>0.02363246123643949</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2980,70 +2980,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.292277591250794</v>
+        <v>-1.292277591250786</v>
       </c>
       <c r="E7" t="n">
         <v>-1.60627723273427</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2369188231549124</v>
+        <v>0.2369188231549107</v>
       </c>
       <c r="G7" t="n">
-        <v>2.504239571973477e-07</v>
+        <v>2.5042395719735e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.557525404993905e-06</v>
+        <v>6.55752540499393e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.403833060547296e-05</v>
+        <v>4.403833060547338e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001944709708000404</v>
+        <v>0.0001944709708000412</v>
       </c>
       <c r="K7" t="n">
-        <v>8.239289168073098e-06</v>
+        <v>8.239289168073076e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.522145043742541e-06</v>
+        <v>2.522145043742545e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>2.519678914462556e-05</v>
+        <v>2.519678914462561e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002664239381850308</v>
+        <v>0.00266423938183662</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0004912265164651931</v>
+        <v>0.0004912265164651954</v>
       </c>
       <c r="P7" t="n">
-        <v>1.660874059878223e-05</v>
+        <v>1.66087405987822e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009015912887515973</v>
+        <v>0.009015912887513515</v>
       </c>
       <c r="R7" t="n">
         <v>6.914641102902019e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.300454012836435e-06</v>
+        <v>3.300454012836477e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007875337957197599</v>
+        <v>0.007875337957198436</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02334079816885376</v>
+        <v>0.02334079816885375</v>
       </c>
       <c r="V7" t="n">
         <v>2.362744815371567e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003047171912796707</v>
+        <v>0.000304717191279671</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01093926732138754</v>
+        <v>0.01093926732138756</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0220765931127416</v>
+        <v>0.02207659311274162</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3064,58 +3064,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.157421776620442</v>
+        <v>-1.157421776620401</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.594531383761507</v>
+        <v>-1.594531383761506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3101834768749292</v>
+        <v>0.310183476874932</v>
       </c>
       <c r="G8" t="n">
-        <v>2.60191542639818e-07</v>
+        <v>2.601915426398179e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.798745828676001e-06</v>
+        <v>6.798745828676002e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.980385718243052e-05</v>
+        <v>5.980385718243096e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002487977476780348</v>
+        <v>0.0002487977476780352</v>
       </c>
       <c r="K8" t="n">
-        <v>1.082933422012096e-05</v>
+        <v>1.082933422012095e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.155360374887882e-06</v>
+        <v>3.155360374885295e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.321850514948562e-05</v>
+        <v>3.321850514948567e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003426553061865885</v>
+        <v>0.003426553061873118</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001625892900298988</v>
+        <v>0.001625892900298989</v>
       </c>
       <c r="P8" t="n">
-        <v>2.152746894981349e-05</v>
+        <v>2.152746894981348e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01524758646021822</v>
+        <v>0.01524758646023521</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001229711754075643</v>
+        <v>0.0001229711754075651</v>
       </c>
       <c r="S8" t="n">
-        <v>4.009776762668648e-06</v>
+        <v>4.00977676266871e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04107363540280808</v>
+        <v>0.04107363540280843</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0274636078008333</v>
+        <v>0.02746360780083333</v>
       </c>
       <c r="V8" t="n">
         <v>2.541194588843778e-06</v>
@@ -3124,10 +3124,10 @@
         <v>0.0003252259760717383</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01201460822552784</v>
+        <v>0.01201460822552787</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02523507340505805</v>
+        <v>0.02523507340505812</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3148,70 +3148,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.286104027422972</v>
+        <v>-1.286104027422996</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.605792974238931</v>
+        <v>-1.605792974238932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2452881084525922</v>
+        <v>0.2452881084525914</v>
       </c>
       <c r="G9" t="n">
-        <v>2.504146146646007e-07</v>
+        <v>2.504146146645995e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>6.556318782835718e-06</v>
+        <v>6.556318782835706e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>4.410949168723157e-05</v>
+        <v>4.410949168723167e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001923390322356383</v>
+        <v>0.0001923390322356375</v>
       </c>
       <c r="K9" t="n">
-        <v>7.805243129140956e-06</v>
+        <v>7.805243129140942e-06</v>
       </c>
       <c r="L9" t="n">
         <v>2.488528586518843e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.462544083629329e-05</v>
+        <v>2.462544083629322e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002448999934092788</v>
+        <v>0.002448999934082491</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0004889631384711481</v>
+        <v>0.0004889631384708728</v>
       </c>
       <c r="P9" t="n">
-        <v>1.625369198364374e-05</v>
+        <v>1.625369198364369e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008731578610435678</v>
+        <v>0.008731578610453639</v>
       </c>
       <c r="R9" t="n">
-        <v>7.040323148520276e-05</v>
+        <v>7.040323148520267e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.314979553935994e-06</v>
+        <v>3.314979553935917e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005601689164160739</v>
+        <v>0.00560168916416057</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02335356750553526</v>
+        <v>0.02335356750553519</v>
       </c>
       <c r="V9" t="n">
-        <v>2.353440918845096e-06</v>
+        <v>2.353440918845094e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003056315554172025</v>
+        <v>0.000305631555417202</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01093500427019157</v>
+        <v>0.01093500427019158</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02216487253146286</v>
+        <v>0.02216487253146285</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -3232,70 +3232,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.325066600036381</v>
+        <v>-1.325066600036364</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.612434062968964</v>
+        <v>-1.612434062968962</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2213564566078987</v>
+        <v>0.2213564566078986</v>
       </c>
       <c r="G10" t="n">
-        <v>2.437057436126674e-07</v>
+        <v>2.437057436126669e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>6.401146711956973e-06</v>
+        <v>6.401146711956965e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>3.690763526469011e-05</v>
+        <v>3.690763526468981e-05</v>
       </c>
       <c r="J10" t="n">
         <v>0.0001591744440864191</v>
       </c>
       <c r="K10" t="n">
-        <v>6.232301462574511e-06</v>
+        <v>6.232301462574491e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>2.038390667617894e-06</v>
+        <v>2.03839066761789e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>2.022753678463053e-05</v>
+        <v>2.02275367846304e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001997654717967101</v>
+        <v>0.001997654717969489</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0003962917553510036</v>
+        <v>0.0003962917553510028</v>
       </c>
       <c r="P10" t="n">
-        <v>1.33859808109951e-05</v>
+        <v>1.338598081099503e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.007125988120674628</v>
+        <v>0.007125988120684126</v>
       </c>
       <c r="R10" t="n">
-        <v>6.153988721056384e-05</v>
+        <v>6.153988721059192e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.896904983858844e-06</v>
+        <v>2.896904983858831e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0036227855866727</v>
+        <v>0.003622785586672703</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02145993041192557</v>
+        <v>0.02145993041192556</v>
       </c>
       <c r="V10" t="n">
         <v>2.238315205429518e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002926020834925043</v>
+        <v>0.0002926020834925045</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01020480014999298</v>
+        <v>0.010204800149993</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02059963552342418</v>
+        <v>0.02059963552342421</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>

--- a/Results/Methanol/methanol climate change remind breakdown results.xlsx
+++ b/Results/Methanol/methanol climate change remind breakdown results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8176128736045802</v>
+        <v>0.8176128736045805</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2672282289984568</v>
+        <v>0.267228228998457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4882558070015925</v>
+        <v>0.4882558070015926</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03017318194979631</v>
+        <v>0.03017318194979638</v>
       </c>
       <c r="H2" t="n">
-        <v>7.508784496133217e-05</v>
+        <v>7.508784496133282e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001186532738769452</v>
+        <v>0.0001186532738769454</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003943937727512739</v>
+        <v>0.0003943937727512733</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000379346935229613</v>
+        <v>0.0003793469352296137</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003479127878982793</v>
+        <v>0.0003479127878982795</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003342013162548133</v>
+        <v>0.0003342013162548144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001200060968002244</v>
+        <v>0.001200060968002248</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910599875576014</v>
+        <v>0.02910599875575992</v>
       </c>
     </row>
     <row r="3">
@@ -569,40 +569,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8051765693971341</v>
+        <v>0.8051765693971339</v>
       </c>
       <c r="E3" t="n">
         <v>0.2671474298486587</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4865842964653778</v>
+        <v>0.4865842964653779</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01979926382768728</v>
+        <v>0.0197992638276873</v>
       </c>
       <c r="H3" t="n">
-        <v>5.953267764265693e-05</v>
+        <v>5.953267764265678e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.720893079672531e-05</v>
+        <v>9.720893079672535e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003309100714395542</v>
+        <v>0.0003309100714395479</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003664982901017471</v>
+        <v>0.0003664982901017472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003031302577696438</v>
+        <v>0.0003031302577696665</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003215116471249632</v>
+        <v>0.0003215116471249627</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00106078872015114</v>
+        <v>0.001060788720151135</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910599866038377</v>
+        <v>0.02910599866038344</v>
       </c>
     </row>
     <row r="4">
@@ -623,28 +623,28 @@
         <v>0.7999564134561892</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2698817205296968</v>
+        <v>0.2698817205296969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4861149770555099</v>
+        <v>0.48611497705551</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01250230121302781</v>
+        <v>0.01250230121302784</v>
       </c>
       <c r="H4" t="n">
-        <v>4.879129851870845e-05</v>
+        <v>4.879129851870834e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>8.2420785038743e-05</v>
+        <v>8.242078503874294e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002873797842738762</v>
+        <v>0.0002873797842738756</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003594026147415705</v>
+        <v>0.0003594026147415707</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002700963798406353</v>
+        <v>0.0002700963798406241</v>
       </c>
       <c r="M4" t="n">
         <v>0.0003109178953228118</v>
@@ -653,7 +653,7 @@
         <v>0.0009924072266302433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0291059986735881</v>
+        <v>0.02910599867358787</v>
       </c>
     </row>
     <row r="5">
@@ -671,40 +671,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7898307847015491</v>
+        <v>0.7898307847015502</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2555559913989692</v>
+        <v>0.2555559913989696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.483810033795798</v>
+        <v>0.4838100337957983</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01890331236210102</v>
+        <v>0.01890331236210105</v>
       </c>
       <c r="H5" t="n">
-        <v>5.63592206783033e-05</v>
+        <v>5.635922067830382e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.415883481072942e-05</v>
+        <v>9.415883481072948e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003182603305252018</v>
+        <v>0.0003182603305252032</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003619665949002915</v>
+        <v>0.0003619665949002921</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002947506833820981</v>
+        <v>0.0002947506833820984</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003144869833526041</v>
+        <v>0.0003144869833526075</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001015466185958884</v>
+        <v>0.001015466185958888</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02910599831107286</v>
+        <v>0.0291059983110733</v>
       </c>
     </row>
     <row r="6">
@@ -725,37 +725,37 @@
         <v>0.7614708455921422</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2465306436778226</v>
+        <v>0.2465306436778228</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4799903697824477</v>
+        <v>0.479990369782448</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003921842988284891</v>
+        <v>0.003921842988284893</v>
       </c>
       <c r="H6" t="n">
-        <v>3.269832815897764e-05</v>
+        <v>3.269832815897751e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>6.357707388553073e-05</v>
+        <v>6.357707388553067e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002203659522448961</v>
+        <v>0.0002203659522448928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003309054335166834</v>
+        <v>0.0003309054335166829</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002272195912850219</v>
+        <v>0.0002272195912851035</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002904568291955275</v>
+        <v>0.0002904568291955264</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007567680393695167</v>
+        <v>0.0007567680393695163</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910599789593082</v>
+        <v>0.02910599789593027</v>
       </c>
     </row>
     <row r="7">
@@ -773,37 +773,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7541786221934</v>
+        <v>0.7541786221933994</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2429012221933689</v>
+        <v>0.242901222193369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4789178129161029</v>
+        <v>0.4789178129161028</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001578342388446875</v>
+        <v>0.001578342388446907</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58350113941555e-05</v>
+        <v>2.583501139415554e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.703150177115056e-05</v>
+        <v>5.703150177115063e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001875225437057094</v>
+        <v>0.000187522543705708</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003066585515984842</v>
+        <v>0.000306658551598484</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002063021768271012</v>
+        <v>0.0002063021768262531</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002788087865749778</v>
+        <v>0.0002788087865749782</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006130883585121079</v>
+        <v>0.0006130883585121091</v>
       </c>
       <c r="O7" t="n">
         <v>0.02910599776509781</v>
@@ -824,40 +824,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7624911818742238</v>
+        <v>0.762491181874222</v>
       </c>
       <c r="E8" t="n">
         <v>0.2415314900677167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4806886961775709</v>
+        <v>0.480688696177572</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009033023779849148</v>
+        <v>0.009033023779849141</v>
       </c>
       <c r="H8" t="n">
-        <v>4.126272957781063e-05</v>
+        <v>4.126272957781069e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.265592233550222e-05</v>
+        <v>7.265592233550216e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002546547806893609</v>
+        <v>0.0002546547806893604</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000343343011969366</v>
+        <v>0.0003433430119693656</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002526229778494624</v>
+        <v>0.0002526229778495081</v>
       </c>
       <c r="M8" t="n">
         <v>0.0002992408204281956</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008681938368657692</v>
+        <v>0.0008681938368657677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02910599776937151</v>
+        <v>0.02910599776936862</v>
       </c>
     </row>
     <row r="9">
@@ -875,40 +875,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7232344761044154</v>
+        <v>0.7232344761044153</v>
       </c>
       <c r="E9" t="n">
         <v>0.2178732829826221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4734956181293406</v>
+        <v>0.4734956181293408</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001065422157181512</v>
+        <v>0.001065422157181537</v>
       </c>
       <c r="H9" t="n">
-        <v>2.563357951726015e-05</v>
+        <v>2.563357951726049e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6407684384502e-05</v>
+        <v>5.640768438450198e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001878255594395179</v>
+        <v>0.0001878255594395169</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003095530133562656</v>
+        <v>0.0003095530133562659</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002059496929954471</v>
+        <v>0.0002059496929957063</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0002792912927835886</v>
+        <v>0.0002792912927835894</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0006294949974389356</v>
+        <v>0.0006294949974389374</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910599701535566</v>
+        <v>0.0291059970153551</v>
       </c>
     </row>
     <row r="10">
@@ -926,40 +926,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7090213199991662</v>
+        <v>0.7090213199991673</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2157640979134274</v>
+        <v>0.2157640979134275</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4621111202396367</v>
+        <v>0.4621111202396369</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0006310792245726907</v>
+        <v>0.0006310792245726921</v>
       </c>
       <c r="H10" t="n">
-        <v>1.941576900401797e-05</v>
+        <v>1.94157690040182e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>5.170881410368868e-05</v>
+        <v>5.170881410368873e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001571588557477467</v>
+        <v>0.0001571588557477462</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002818120950957679</v>
+        <v>0.0002818120950957683</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001878502249644482</v>
+        <v>0.0001878502249654532</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002604720881249709</v>
+        <v>0.000260472088124971</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0004506075567126557</v>
+        <v>0.0004506075567126571</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910599721777607</v>
+        <v>0.02910599721777596</v>
       </c>
     </row>
   </sheetData>
@@ -1063,40 +1063,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5153058104885051</v>
+        <v>0.5153058104885052</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2672282289984568</v>
+        <v>0.267228228998457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1859487363971419</v>
+        <v>0.185948736397142</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03017318194979631</v>
+        <v>0.03017318194979638</v>
       </c>
       <c r="H2" t="n">
-        <v>7.508784496133217e-05</v>
+        <v>7.508784496133282e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001186532738769452</v>
+        <v>0.0001186532738769454</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003943937727512739</v>
+        <v>0.0003943937727512733</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000379346935229613</v>
+        <v>0.0003793469352296137</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003479127878982793</v>
+        <v>0.0003479127878982795</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003342013162548133</v>
+        <v>0.0003342013162548144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001200060968002244</v>
+        <v>0.001200060968002248</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02910600624413567</v>
+        <v>0.02910600624413534</v>
       </c>
     </row>
     <row r="3">
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4834208114528942</v>
+        <v>0.4834208114528937</v>
       </c>
       <c r="E3" t="n">
         <v>0.2671474298486587</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1648285305510012</v>
+        <v>0.1648285305510009</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01979926382768728</v>
+        <v>0.0197992638276873</v>
       </c>
       <c r="H3" t="n">
-        <v>5.953267764265693e-05</v>
+        <v>5.953267764265678e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.720893079672531e-05</v>
+        <v>9.720893079672535e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003309100714395542</v>
+        <v>0.0003309100714395479</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003664982901017471</v>
+        <v>0.0003664982901017472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003031302577696438</v>
+        <v>0.0003031302577696665</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003215116471249632</v>
+        <v>0.0003215116471249627</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00106078872015114</v>
+        <v>0.001060788720151135</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02910600663052049</v>
+        <v>0.02910600663052038</v>
       </c>
     </row>
     <row r="4">
@@ -1165,31 +1165,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4646724527004893</v>
+        <v>0.4646724527004895</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2698817205296968</v>
+        <v>0.2698817205296969</v>
       </c>
       <c r="F4" t="n">
         <v>0.1508310079945716</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01250230121302781</v>
+        <v>0.01250230121302784</v>
       </c>
       <c r="H4" t="n">
-        <v>4.879129851870845e-05</v>
+        <v>4.879129851870834e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>8.2420785038743e-05</v>
+        <v>8.242078503874294e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002873797842738762</v>
+        <v>0.0002873797842738756</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003594026147415705</v>
+        <v>0.0003594026147415707</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002700963798406353</v>
+        <v>0.0002700963798406241</v>
       </c>
       <c r="M4" t="n">
         <v>0.0003109178953228118</v>
@@ -1216,40 +1216,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4654479939243053</v>
+        <v>0.4654479939243054</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2555559913989692</v>
+        <v>0.2555559913989696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1594272349833451</v>
+        <v>0.1594272349833453</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01890331236210102</v>
+        <v>0.01890331236210105</v>
       </c>
       <c r="H5" t="n">
-        <v>5.63592206783033e-05</v>
+        <v>5.635922067830382e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>9.415883481072942e-05</v>
+        <v>9.415883481072948e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003182603305252018</v>
+        <v>0.0003182603305252032</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003619665949002915</v>
+        <v>0.0003619665949002921</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002947506833820981</v>
+        <v>0.0002947506833820984</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003144869833526041</v>
+        <v>0.0003144869833526075</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001015466185958884</v>
+        <v>0.001015466185958888</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0291060063462818</v>
+        <v>0.02910600634628141</v>
       </c>
     </row>
     <row r="6">
@@ -1267,40 +1267,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4076584096938252</v>
+        <v>0.4076584096938253</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2465306436778226</v>
+        <v>0.2465306436778228</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1261779251199269</v>
+        <v>0.126177925119927</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003921842988284891</v>
+        <v>0.003921842988284893</v>
       </c>
       <c r="H6" t="n">
-        <v>3.269832815897764e-05</v>
+        <v>3.269832815897751e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>6.357707388553073e-05</v>
+        <v>6.357707388553067e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002203659522448961</v>
+        <v>0.0002203659522448928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003309054335166834</v>
+        <v>0.0003309054335166829</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002272195912850219</v>
+        <v>0.0002272195912851035</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002904568291955275</v>
+        <v>0.0002904568291955264</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007567680393695167</v>
+        <v>0.0007567680393695163</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02910600666013463</v>
+        <v>0.02910600666013441</v>
       </c>
     </row>
     <row r="7">
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3955308079157695</v>
+        <v>0.3955308079157697</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2429012221933689</v>
+        <v>0.242901222193369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202699897544925</v>
+        <v>0.1202699897544926</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001578342388446875</v>
+        <v>0.001578342388446907</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58350113941555e-05</v>
+        <v>2.583501139415554e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.703150177115056e-05</v>
+        <v>5.703150177115063e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001875225437057094</v>
+        <v>0.000187522543705708</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003066585515984842</v>
+        <v>0.000306658551598484</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002063021768271012</v>
+        <v>0.0002063021768262531</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002788087865749778</v>
+        <v>0.0002788087865749782</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0006130883585121079</v>
+        <v>0.0006130883585121091</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02910600664907753</v>
+        <v>0.02910600664907836</v>
       </c>
     </row>
     <row r="8">
@@ -1369,40 +1369,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4168387202451334</v>
+        <v>0.4168387202451332</v>
       </c>
       <c r="E8" t="n">
         <v>0.2415314900677167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1350362259864091</v>
+        <v>0.135036225986409</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009033023779849148</v>
+        <v>0.009033023779849141</v>
       </c>
       <c r="H8" t="n">
-        <v>4.126272957781063e-05</v>
+        <v>4.126272957781069e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.265592233550222e-05</v>
+        <v>7.265592233550216e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002546547806893609</v>
+        <v>0.0002546547806893604</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000343343011969366</v>
+        <v>0.0003433430119693656</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002526229778494624</v>
+        <v>0.0002526229778495081</v>
       </c>
       <c r="M8" t="n">
         <v>0.0002992408204281956</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008681938368657692</v>
+        <v>0.0008681938368657677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.029106006331443</v>
+        <v>0.02910600633144278</v>
       </c>
     </row>
     <row r="9">
@@ -1420,40 +1420,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3612501119575768</v>
+        <v>0.3612501119575772</v>
       </c>
       <c r="E9" t="n">
         <v>0.2178732829826221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1115112450158727</v>
+        <v>0.111511245015873</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001065422157181512</v>
+        <v>0.001065422157181537</v>
       </c>
       <c r="H9" t="n">
-        <v>2.563357951726015e-05</v>
+        <v>2.563357951726049e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6407684384502e-05</v>
+        <v>5.640768438450198e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001878255594395179</v>
+        <v>0.0001878255594395169</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0003095530133562656</v>
+        <v>0.0003095530133562659</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002059496929954471</v>
+        <v>0.0002059496929957063</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0002792912927835886</v>
+        <v>0.0002792912927835894</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0006294949974389356</v>
+        <v>0.0006294949974389374</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02910600598198498</v>
+        <v>0.02910600598198482</v>
       </c>
     </row>
     <row r="10">
@@ -1471,40 +1471,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3568511086824415</v>
+        <v>0.3568511086824421</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2157640979134274</v>
+        <v>0.2157640979134275</v>
       </c>
       <c r="F10" t="n">
         <v>0.1099409001993871</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0006310792245726907</v>
+        <v>0.0006310792245726921</v>
       </c>
       <c r="H10" t="n">
-        <v>1.941576900401797e-05</v>
+        <v>1.94157690040182e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>5.170881410368868e-05</v>
+        <v>5.170881410368873e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001571588557477467</v>
+        <v>0.0001571588557477462</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002818120950957679</v>
+        <v>0.0002818120950957683</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001878502249644482</v>
+        <v>0.0001878502249654532</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002604720881249709</v>
+        <v>0.000260472088124971</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0004506075567126557</v>
+        <v>0.0004506075567126571</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02910600594130097</v>
+        <v>0.02910600594130047</v>
       </c>
     </row>
   </sheetData>
@@ -1663,70 +1663,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.019141429889652</v>
+        <v>-1.01914142988966</v>
       </c>
       <c r="E2" t="n">
         <v>-1.559063565100552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2854433532441244</v>
+        <v>0.2854433532441241</v>
       </c>
       <c r="G2" t="n">
-        <v>2.761669111764112e-07</v>
+        <v>2.761669111764123e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.583610202153034e-06</v>
+        <v>7.583610202153032e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.262056182651773e-05</v>
+        <v>9.262056182651788e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003411598654679199</v>
+        <v>0.0003411598654679212</v>
       </c>
       <c r="K2" t="n">
-        <v>2.006979350318942e-05</v>
+        <v>2.006979350325126e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.017943967169584e-05</v>
+        <v>1.017943967169635e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.94118722674492e-05</v>
+        <v>4.94118722674493e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00630245184793262</v>
+        <v>0.006302451847932483</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002426031438041062</v>
+        <v>0.002426031438041066</v>
       </c>
       <c r="P2" t="n">
-        <v>3.091245712846872e-05</v>
+        <v>3.09124571284688e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02986595231012155</v>
+        <v>0.02986595231011676</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001628288364327003</v>
+        <v>0.0001628288364327005</v>
       </c>
       <c r="S2" t="n">
-        <v>5.169039934467407e-06</v>
+        <v>5.16903993446742e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1350987264549083</v>
+        <v>0.1350987264549085</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0354706761402051</v>
+        <v>0.03547067614020507</v>
       </c>
       <c r="V2" t="n">
-        <v>2.991450848324466e-06</v>
+        <v>2.991450848324465e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003809876879135905</v>
+        <v>0.0003809876879135904</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01386906203123719</v>
+        <v>0.01386906203123717</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0303416526368951</v>
+        <v>0.03034165263689509</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1747,58 +1747,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.124205631353592</v>
+        <v>-1.124205631353546</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.567329179523424</v>
+        <v>-1.567329179523421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2515327988334882</v>
+        <v>0.2515327988334884</v>
       </c>
       <c r="G3" t="n">
-        <v>2.692495566807682e-07</v>
+        <v>2.692495566807699e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>7.289007861914838e-06</v>
+        <v>7.289007861914814e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.771186780404286e-05</v>
+        <v>7.77118678040429e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002922211285163694</v>
+        <v>0.0002922211285163688</v>
       </c>
       <c r="K3" t="n">
-        <v>1.51502689945132e-05</v>
+        <v>1.515026899451322e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.824841845708134e-06</v>
+        <v>7.824841845711238e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.000381873355774e-05</v>
+        <v>4.000381873355762e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004761391042061684</v>
+        <v>0.00476139104206992</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001579801963900486</v>
+        <v>0.001579801963900483</v>
       </c>
       <c r="P3" t="n">
-        <v>2.539884965996654e-05</v>
+        <v>2.539884965996649e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02278372254080168</v>
+        <v>0.02278372254081502</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001209232842262595</v>
+        <v>0.0001209232842262593</v>
       </c>
       <c r="S3" t="n">
-        <v>4.644714719611884e-06</v>
+        <v>4.644714719611873e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08896275042748486</v>
+        <v>0.08896275042748476</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03156397257714592</v>
+        <v>0.03156397257714597</v>
       </c>
       <c r="V3" t="n">
         <v>2.77224586507985e-06</v>
@@ -1807,10 +1807,10 @@
         <v>0.0003588791288868769</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01298307465424493</v>
+        <v>0.012983074654245</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02800291181003578</v>
+        <v>0.02800291181003583</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1831,70 +1831,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.1899780971833</v>
+        <v>-1.18997809718326</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.573219727399013</v>
+        <v>-1.573219727399016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.236039929963854</v>
+        <v>0.2360399299638536</v>
       </c>
       <c r="G4" t="n">
-        <v>2.648164763026866e-07</v>
+        <v>2.648164763026858e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>7.073304207949564e-06</v>
+        <v>7.073304207949533e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>6.748909063991802e-05</v>
+        <v>6.748909063991783e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002624910296197435</v>
+        <v>0.0002624910296197441</v>
       </c>
       <c r="K4" t="n">
-        <v>1.200007627857962e-05</v>
+        <v>1.200007627857961e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.828183141979014e-06</v>
+        <v>5.828183141919369e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.502950038710193e-05</v>
+        <v>3.50295003871019e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003567598529931511</v>
+        <v>0.003567598529930878</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001112333318218445</v>
+        <v>0.001112333318218446</v>
       </c>
       <c r="P4" t="n">
         <v>2.249750005340634e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01777924469769828</v>
+        <v>0.0177792446976969</v>
       </c>
       <c r="R4" t="n">
-        <v>9.599275579775146e-05</v>
+        <v>9.599275579775131e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.232420971918214e-06</v>
+        <v>4.232420971918211e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05651169876996144</v>
+        <v>0.05651169876996135</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02877680311982532</v>
+        <v>0.02877680311982529</v>
       </c>
       <c r="V4" t="n">
-        <v>2.629238739657008e-06</v>
+        <v>2.62923873965701e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003415158359136905</v>
+        <v>0.0003415158359136894</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01229729657868709</v>
+        <v>0.01229729657868711</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02629964727778472</v>
+        <v>0.0262996472777848</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1915,67 +1915,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.14790154733987</v>
+        <v>-1.1479015473399</v>
       </c>
       <c r="E5" t="n">
         <v>-1.588281614445171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2553969155297909</v>
+        <v>0.2553969155297917</v>
       </c>
       <c r="G5" t="n">
-        <v>2.665204581106058e-07</v>
+        <v>2.665204581106083e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.16346854620395e-06</v>
+        <v>7.163468546203994e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>7.474116646088053e-05</v>
+        <v>7.474116646088058e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002806588187578473</v>
+        <v>0.0002806588187578487</v>
       </c>
       <c r="K5" t="n">
-        <v>1.285068047712329e-05</v>
+        <v>1.285068047712334e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.837409510672719e-06</v>
+        <v>3.837409510672586e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.775735238594349e-05</v>
+        <v>3.775735238594364e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004201264662515718</v>
+        <v>0.004201264662512122</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001938514208323963</v>
+        <v>0.001938514208323967</v>
       </c>
       <c r="P5" t="n">
-        <v>2.409764181356524e-05</v>
+        <v>2.409764181356534e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02201689862766348</v>
+        <v>0.02201689862771514</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001398131546922783</v>
+        <v>0.0001398131546922787</v>
       </c>
       <c r="S5" t="n">
-        <v>4.48188381062693e-06</v>
+        <v>4.481883810626948e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08497176690150429</v>
+        <v>0.08497176690150438</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03079146666181661</v>
+        <v>0.03079146666181665</v>
       </c>
       <c r="V5" t="n">
-        <v>2.648566676086905e-06</v>
+        <v>2.648566676086908e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003357775868105736</v>
+        <v>0.0003357775868105738</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01262194038716204</v>
+        <v>0.01262194038716203</v>
       </c>
       <c r="Y5" t="n">
         <v>0.02751716983688129</v>
@@ -1999,70 +1999,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.297360266472128</v>
+        <v>-1.29736026647213</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.600390566661067</v>
+        <v>-1.600390566661068</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2082320883459166</v>
+        <v>0.2082320883459161</v>
       </c>
       <c r="G6" t="n">
         <v>2.563161045457806e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>6.671573010948768e-06</v>
+        <v>6.671573010948771e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.175137062123434e-05</v>
+        <v>5.175137062123329e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002235525539087687</v>
+        <v>0.0002235525539094354</v>
       </c>
       <c r="K6" t="n">
-        <v>9.585839132261671e-06</v>
+        <v>9.585839132261629e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>2.908648220078291e-06</v>
+        <v>2.908648220079696e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.939049108510493e-05</v>
+        <v>2.939049108510498e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00310293708002811</v>
+        <v>0.003102937080027626</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006213565869026663</v>
+        <v>0.0006213565869026614</v>
       </c>
       <c r="P6" t="n">
-        <v>1.924853846726155e-05</v>
+        <v>1.924853846726148e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01146407561192377</v>
+        <v>0.01146407561190298</v>
       </c>
       <c r="R6" t="n">
-        <v>8.45640926161655e-05</v>
+        <v>8.456409261616575e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.677714219969792e-06</v>
+        <v>3.677714219969842e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01833026327061504</v>
+        <v>0.01833026327061528</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02533583789501207</v>
+        <v>0.02533583789501204</v>
       </c>
       <c r="V6" t="n">
-        <v>2.462720827515053e-06</v>
+        <v>2.462720827515054e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003160411495889312</v>
+        <v>0.0003160411495889311</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01156113660926156</v>
+        <v>0.0115611366092616</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02363246123643949</v>
+        <v>0.02363246123643938</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2083,67 +2083,67 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.341601046001074</v>
+        <v>-1.341601046001031</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.60627723273427</v>
+        <v>-1.606277232734268</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1875953683857767</v>
+        <v>0.1875953683857771</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5042395719735e-07</v>
+        <v>2.504239571973465e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.55752540499393e-06</v>
+        <v>6.557525404993923e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.403833060547338e-05</v>
+        <v>4.403833060547305e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001944709708000412</v>
+        <v>0.0001944709708000409</v>
       </c>
       <c r="K7" t="n">
-        <v>8.239289168073076e-06</v>
+        <v>8.239289168073086e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.522145043742545e-06</v>
+        <v>2.522145043736081e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>2.519678914462561e-05</v>
+        <v>2.519678914462564e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00266423938183662</v>
+        <v>0.002664239381850302</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0004912265164651954</v>
+        <v>0.0004912265164651966</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66087405987822e-05</v>
+        <v>1.660874059878223e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009015912887513515</v>
+        <v>0.009015912887538611</v>
       </c>
       <c r="R7" t="n">
-        <v>6.914641102902019e-05</v>
+        <v>6.914641102902021e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.300454012836477e-06</v>
+        <v>3.300454012836465e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007875337957198436</v>
+        <v>0.00787533795719818</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02334079816885375</v>
+        <v>0.02334079816885372</v>
       </c>
       <c r="V7" t="n">
-        <v>2.362744815371567e-06</v>
+        <v>2.362744815371569e-06</v>
       </c>
       <c r="W7" t="n">
         <v>0.000304717191279671</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01093926732138756</v>
+        <v>0.01093926732138755</v>
       </c>
       <c r="Y7" t="n">
         <v>0.02207659311274162</v>
@@ -2167,70 +2167,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.232574613344944</v>
+        <v>-1.232574613344954</v>
       </c>
       <c r="E8" t="n">
         <v>-1.594531383761506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2350306401216745</v>
+        <v>0.2350306401216747</v>
       </c>
       <c r="G8" t="n">
-        <v>2.601915426398179e-07</v>
+        <v>2.601915426398153e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.798745828676002e-06</v>
+        <v>6.798745828675992e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.980385718243096e-05</v>
+        <v>5.980385718243082e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002487977476780352</v>
+        <v>0.0002487977476782778</v>
       </c>
       <c r="K8" t="n">
-        <v>1.082933422012095e-05</v>
+        <v>1.082933422012094e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.155360374885295e-06</v>
+        <v>3.155360374885292e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.321850514948567e-05</v>
+        <v>3.321850514948556e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003426553061873118</v>
+        <v>0.003426553061883632</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001625892900298989</v>
+        <v>0.001625892900298988</v>
       </c>
       <c r="P8" t="n">
-        <v>2.152746894981348e-05</v>
+        <v>2.152746894981344e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01524758646023521</v>
+        <v>0.01524758646019238</v>
       </c>
       <c r="R8" t="n">
         <v>0.0001229711754075651</v>
       </c>
       <c r="S8" t="n">
-        <v>4.00977676266871e-06</v>
+        <v>4.009776762668659e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04107363540280843</v>
+        <v>0.04107363540280832</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02746360780083333</v>
+        <v>0.02746360780083329</v>
       </c>
       <c r="V8" t="n">
-        <v>2.541194588843778e-06</v>
+        <v>2.541194588843777e-06</v>
       </c>
       <c r="W8" t="n">
         <v>0.0003252259760717383</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01201460822552787</v>
+        <v>0.01201460822552783</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02523507340505812</v>
+        <v>0.0252350734050581</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -2251,70 +2251,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.34226426262418</v>
+        <v>-1.342264262624166</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.605792974238932</v>
+        <v>-1.605792974238931</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1891278732299564</v>
+        <v>0.1891278732299554</v>
       </c>
       <c r="G9" t="n">
-        <v>2.504146146645995e-07</v>
+        <v>2.504146146645996e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>6.556318782835706e-06</v>
+        <v>6.556318782835715e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>4.410949168723167e-05</v>
+        <v>4.410949168723147e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001923390322356375</v>
+        <v>0.000192339032235638</v>
       </c>
       <c r="K9" t="n">
-        <v>7.805243129140942e-06</v>
+        <v>7.805243129140941e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>2.488528586518843e-06</v>
+        <v>2.488528586540938e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.462544083629322e-05</v>
+        <v>2.462544083629321e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002448999934082491</v>
+        <v>0.002448999934097853</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0004889631384708728</v>
+        <v>0.0004889631384711468</v>
       </c>
       <c r="P9" t="n">
-        <v>1.625369198364369e-05</v>
+        <v>1.625369198364372e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008731578610453639</v>
+        <v>0.00873157861044176</v>
       </c>
       <c r="R9" t="n">
-        <v>7.040323148520267e-05</v>
+        <v>7.040323148520272e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.314979553935917e-06</v>
+        <v>3.314979553935959e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00560168916416057</v>
+        <v>0.005601689164160765</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02335356750553519</v>
+        <v>0.02335356750553523</v>
       </c>
       <c r="V9" t="n">
-        <v>2.353440918845094e-06</v>
+        <v>2.353440918845096e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.000305631555417202</v>
+        <v>0.0003056315554172028</v>
       </c>
       <c r="X9" t="n">
         <v>0.01093500427019158</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02216487253146285</v>
+        <v>0.02216487253146281</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2335,70 +2335,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.381333991894089</v>
+        <v>-1.381333991894111</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.612434062968962</v>
+        <v>-1.612434062968964</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1650890647286752</v>
+        <v>0.165089064728676</v>
       </c>
       <c r="G10" t="n">
-        <v>2.437057436126669e-07</v>
+        <v>2.437057436126683e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>6.401146711956965e-06</v>
+        <v>6.40114671195703e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>3.690763526468981e-05</v>
+        <v>3.690763526469016e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001591744440864191</v>
+        <v>0.0001591744440864193</v>
       </c>
       <c r="K10" t="n">
-        <v>6.232301462574491e-06</v>
+        <v>6.232301462574509e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>2.03839066761789e-06</v>
+        <v>2.038390667617891e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>2.02275367846304e-05</v>
+        <v>2.022753678463039e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001997654717969489</v>
+        <v>0.001997654717965398</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0003962917553510028</v>
+        <v>0.0003962917553510044</v>
       </c>
       <c r="P10" t="n">
-        <v>1.338598081099503e-05</v>
+        <v>1.338598081099508e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.007125988120684126</v>
+        <v>0.007125988120666061</v>
       </c>
       <c r="R10" t="n">
-        <v>6.153988721059192e-05</v>
+        <v>6.1539887210564e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.896904983858831e-06</v>
+        <v>2.896904983858827e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.003622785586672703</v>
+        <v>0.003622785586672868</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02145993041192556</v>
+        <v>0.02145993041192557</v>
       </c>
       <c r="V10" t="n">
-        <v>2.238315205429518e-06</v>
+        <v>2.238315205429519e-06</v>
       </c>
       <c r="W10" t="n">
         <v>0.0002926020834925045</v>
       </c>
       <c r="X10" t="n">
-        <v>0.010204800149993</v>
+        <v>0.01020480014999298</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02059963552342421</v>
+        <v>0.02059963552342418</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2560,70 +2560,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.9031709771374251</v>
+        <v>-0.9031709771374379</v>
       </c>
       <c r="E2" t="n">
         <v>-1.559063565100552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4014138060406495</v>
+        <v>0.4014138060406497</v>
       </c>
       <c r="G2" t="n">
-        <v>2.761669111764112e-07</v>
+        <v>2.761669111764123e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.583610202153034e-06</v>
+        <v>7.583610202153032e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>9.262056182651773e-05</v>
+        <v>9.262056182651788e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003411598654679199</v>
+        <v>0.0003411598654679212</v>
       </c>
       <c r="K2" t="n">
-        <v>2.006979350318942e-05</v>
+        <v>2.006979350325126e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.017943967169584e-05</v>
+        <v>1.017943967169635e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>4.94118722674492e-05</v>
+        <v>4.94118722674493e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00630245184793262</v>
+        <v>0.006302451847932483</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002426031438041062</v>
+        <v>0.002426031438041066</v>
       </c>
       <c r="P2" t="n">
-        <v>3.091245712846872e-05</v>
+        <v>3.09124571284688e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02986595231012155</v>
+        <v>0.02986595231011676</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001628288364327003</v>
+        <v>0.0001628288364327005</v>
       </c>
       <c r="S2" t="n">
-        <v>5.169039934467407e-06</v>
+        <v>5.16903993446742e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1350987264549083</v>
+        <v>0.1350987264549085</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0354706761402051</v>
+        <v>0.03547067614020507</v>
       </c>
       <c r="V2" t="n">
-        <v>2.991450848324466e-06</v>
+        <v>2.991450848324465e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0003809876879135905</v>
+        <v>0.0003809876879135904</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01386906203123719</v>
+        <v>0.01386906203123717</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0303416526368951</v>
+        <v>0.03034165263689509</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -2644,58 +2644,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.051593715662021</v>
+        <v>-1.051593715661995</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.567329179523424</v>
+        <v>-1.567329179523421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.324144714552804</v>
+        <v>0.3241447145528035</v>
       </c>
       <c r="G3" t="n">
-        <v>2.692495566807682e-07</v>
+        <v>2.692495566807699e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>7.289007861914838e-06</v>
+        <v>7.289007861914814e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.771186780404286e-05</v>
+        <v>7.77118678040429e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002922211285163694</v>
+        <v>0.0002922211285163688</v>
       </c>
       <c r="K3" t="n">
-        <v>1.51502689945132e-05</v>
+        <v>1.515026899451322e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.824841845708134e-06</v>
+        <v>7.824841845711238e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.000381873355774e-05</v>
+        <v>4.000381873355762e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004761391042061684</v>
+        <v>0.00476139104206992</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001579801963900486</v>
+        <v>0.001579801963900483</v>
       </c>
       <c r="P3" t="n">
-        <v>2.539884965996654e-05</v>
+        <v>2.539884965996649e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02278372254080168</v>
+        <v>0.02278372254081502</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001209232842262595</v>
+        <v>0.0001209232842262593</v>
       </c>
       <c r="S3" t="n">
-        <v>4.644714719611884e-06</v>
+        <v>4.644714719611873e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08896275042748486</v>
+        <v>0.08896275042748476</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03156397257714592</v>
+        <v>0.03156397257714597</v>
       </c>
       <c r="V3" t="n">
         <v>2.77224586507985e-06</v>
@@ -2704,10 +2704,10 @@
         <v>0.0003588791288868769</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01298307465424493</v>
+        <v>0.012983074654245</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02800291181003578</v>
+        <v>0.02800291181003583</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2728,70 +2728,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.141097579793108</v>
+        <v>-1.141097579793124</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.573219727399013</v>
+        <v>-1.573219727399016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2849204473726631</v>
+        <v>0.2849204473726633</v>
       </c>
       <c r="G4" t="n">
-        <v>2.648164763026866e-07</v>
+        <v>2.648164763026858e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>7.073304207949564e-06</v>
+        <v>7.073304207949533e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>6.748909063991802e-05</v>
+        <v>6.748909063991783e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002624910296197435</v>
+        <v>0.0002624910296197441</v>
       </c>
       <c r="K4" t="n">
-        <v>1.200007627857962e-05</v>
+        <v>1.200007627857961e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.828183141979014e-06</v>
+        <v>5.828183141919369e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.502950038710193e-05</v>
+        <v>3.50295003871019e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003567598529931511</v>
+        <v>0.003567598529930878</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001112333318218445</v>
+        <v>0.001112333318218446</v>
       </c>
       <c r="P4" t="n">
         <v>2.249750005340634e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01777924469769828</v>
+        <v>0.0177792446976969</v>
       </c>
       <c r="R4" t="n">
-        <v>9.599275579775146e-05</v>
+        <v>9.599275579775131e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.232420971918214e-06</v>
+        <v>4.232420971918211e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05651169876996144</v>
+        <v>0.05651169876996135</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02877680311982532</v>
+        <v>0.02877680311982529</v>
       </c>
       <c r="V4" t="n">
-        <v>2.629238739657008e-06</v>
+        <v>2.62923873965701e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0003415158359136905</v>
+        <v>0.0003415158359136894</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01229729657868709</v>
+        <v>0.01229729657868711</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02629964727778472</v>
+        <v>0.0262996472777848</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -2812,67 +2812,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.055520381490162</v>
+        <v>-1.055520381490168</v>
       </c>
       <c r="E5" t="n">
         <v>-1.588281614445171</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3477780814148119</v>
+        <v>0.3477780814148132</v>
       </c>
       <c r="G5" t="n">
-        <v>2.665204581106058e-07</v>
+        <v>2.665204581106083e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.16346854620395e-06</v>
+        <v>7.163468546203994e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>7.474116646088053e-05</v>
+        <v>7.474116646088058e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002806588187578473</v>
+        <v>0.0002806588187578487</v>
       </c>
       <c r="K5" t="n">
-        <v>1.285068047712329e-05</v>
+        <v>1.285068047712334e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.837409510672719e-06</v>
+        <v>3.837409510672586e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.775735238594349e-05</v>
+        <v>3.775735238594364e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004201264662515718</v>
+        <v>0.004201264662512122</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001938514208323963</v>
+        <v>0.001938514208323967</v>
       </c>
       <c r="P5" t="n">
-        <v>2.409764181356524e-05</v>
+        <v>2.409764181356534e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02201689862766348</v>
+        <v>0.02201689862771514</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001398131546922783</v>
+        <v>0.0001398131546922787</v>
       </c>
       <c r="S5" t="n">
-        <v>4.48188381062693e-06</v>
+        <v>4.481883810626948e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08497176690150429</v>
+        <v>0.08497176690150438</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03079146666181661</v>
+        <v>0.03079146666181665</v>
       </c>
       <c r="V5" t="n">
-        <v>2.648566676086905e-06</v>
+        <v>2.648566676086908e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0003357775868105736</v>
+        <v>0.0003357775868105738</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01262194038716204</v>
+        <v>0.01262194038716203</v>
       </c>
       <c r="Y5" t="n">
         <v>0.02751716983688129</v>
@@ -2896,70 +2896,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.242720704062578</v>
+        <v>-1.242720704062611</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.600390566661067</v>
+        <v>-1.600390566661068</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2628716507763376</v>
+        <v>0.2628716507763377</v>
       </c>
       <c r="G6" t="n">
         <v>2.563161045457806e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>6.671573010948768e-06</v>
+        <v>6.671573010948771e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.175137062123434e-05</v>
+        <v>5.175137062123329e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002235525539087687</v>
+        <v>0.0002235525539094354</v>
       </c>
       <c r="K6" t="n">
-        <v>9.585839132261671e-06</v>
+        <v>9.585839132261629e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>2.908648220078291e-06</v>
+        <v>2.908648220079696e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.939049108510493e-05</v>
+        <v>2.939049108510498e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00310293708002811</v>
+        <v>0.003102937080027626</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006213565869026663</v>
+        <v>0.0006213565869026614</v>
       </c>
       <c r="P6" t="n">
-        <v>1.924853846726155e-05</v>
+        <v>1.924853846726148e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01146407561192377</v>
+        <v>0.01146407561190298</v>
       </c>
       <c r="R6" t="n">
-        <v>8.45640926161655e-05</v>
+        <v>8.456409261616575e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>3.677714219969792e-06</v>
+        <v>3.677714219969842e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01833026327061504</v>
+        <v>0.01833026327061528</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02533583789501207</v>
+        <v>0.02533583789501204</v>
       </c>
       <c r="V6" t="n">
-        <v>2.462720827515053e-06</v>
+        <v>2.462720827515054e-06</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003160411495889312</v>
+        <v>0.0003160411495889311</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01156113660926156</v>
+        <v>0.0115611366092616</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02363246123643949</v>
+        <v>0.02363246123643938</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -2980,67 +2980,67 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.292277591250786</v>
+        <v>-1.292277591250767</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.60627723273427</v>
+        <v>-1.606277232734268</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2369188231549107</v>
+        <v>0.2369188231549117</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5042395719735e-07</v>
+        <v>2.504239571973465e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.55752540499393e-06</v>
+        <v>6.557525404993923e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>4.403833060547338e-05</v>
+        <v>4.403833060547305e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001944709708000412</v>
+        <v>0.0001944709708000409</v>
       </c>
       <c r="K7" t="n">
-        <v>8.239289168073076e-06</v>
+        <v>8.239289168073086e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.522145043742545e-06</v>
+        <v>2.522145043736081e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>2.519678914462561e-05</v>
+        <v>2.519678914462564e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00266423938183662</v>
+        <v>0.002664239381850302</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0004912265164651954</v>
+        <v>0.0004912265164651966</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66087405987822e-05</v>
+        <v>1.660874059878223e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009015912887513515</v>
+        <v>0.009015912887538611</v>
       </c>
       <c r="R7" t="n">
-        <v>6.914641102902019e-05</v>
+        <v>6.914641102902021e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.300454012836477e-06</v>
+        <v>3.300454012836465e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007875337957198436</v>
+        <v>0.00787533795719818</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02334079816885375</v>
+        <v>0.02334079816885372</v>
       </c>
       <c r="V7" t="n">
-        <v>2.362744815371567e-06</v>
+        <v>2.362744815371569e-06</v>
       </c>
       <c r="W7" t="n">
         <v>0.000304717191279671</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01093926732138756</v>
+        <v>0.01093926732138755</v>
       </c>
       <c r="Y7" t="n">
         <v>0.02207659311274162</v>
@@ -3064,70 +3064,70 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.157421776620401</v>
+        <v>-1.157421776620442</v>
       </c>
       <c r="E8" t="n">
         <v>-1.594531383761506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.310183476874932</v>
+        <v>0.3101834768749305</v>
       </c>
       <c r="G8" t="n">
-        <v>2.601915426398179e-07</v>
+        <v>2.601915426398153e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.798745828676002e-06</v>
+        <v>6.798745828675992e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>5.980385718243096e-05</v>
+        <v>5.980385718243082e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002487977476780352</v>
+        <v>0.0002487977476782778</v>
       </c>
       <c r="K8" t="n">
-        <v>1.082933422012095e-05</v>
+        <v>1.082933422012094e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.155360374885295e-06</v>
+        <v>3.155360374885292e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.321850514948567e-05</v>
+        <v>3.321850514948556e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003426553061873118</v>
+        <v>0.003426553061883632</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001625892900298989</v>
+        <v>0.001625892900298988</v>
       </c>
       <c r="P8" t="n">
-        <v>2.152746894981348e-05</v>
+        <v>2.152746894981344e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01524758646023521</v>
+        <v>0.01524758646019238</v>
       </c>
       <c r="R8" t="n">
         <v>0.0001229711754075651</v>
       </c>
       <c r="S8" t="n">
-        <v>4.00977676266871e-06</v>
+        <v>4.009776762668659e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04107363540280843</v>
+        <v>0.04107363540280832</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02746360780083333</v>
+        <v>0.02746360780083329</v>
       </c>
       <c r="V8" t="n">
-        <v>2.541194588843778e-06</v>
+        <v>2.541194588843777e-06</v>
       </c>
       <c r="W8" t="n">
         <v>0.0003252259760717383</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01201460822552787</v>
+        <v>0.01201460822552783</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02523507340505812</v>
+        <v>0.0252350734050581</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -3148,70 +3148,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.286104027422996</v>
+        <v>-1.286104027422981</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.605792974238932</v>
+        <v>-1.605792974238931</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2452881084525914</v>
+        <v>0.2452881084525916</v>
       </c>
       <c r="G9" t="n">
-        <v>2.504146146645995e-07</v>
+        <v>2.504146146645996e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>6.556318782835706e-06</v>
+        <v>6.556318782835715e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>4.410949168723167e-05</v>
+        <v>4.410949168723147e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001923390322356375</v>
+        <v>0.000192339032235638</v>
       </c>
       <c r="K9" t="n">
-        <v>7.805243129140942e-06</v>
+        <v>7.805243129140941e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>2.488528586518843e-06</v>
+        <v>2.488528586540938e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.462544083629322e-05</v>
+        <v>2.462544083629321e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002448999934082491</v>
+        <v>0.002448999934097853</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0004889631384708728</v>
+        <v>0.0004889631384711468</v>
       </c>
       <c r="P9" t="n">
-        <v>1.625369198364369e-05</v>
+        <v>1.625369198364372e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008731578610453639</v>
+        <v>0.00873157861044176</v>
       </c>
       <c r="R9" t="n">
-        <v>7.040323148520267e-05</v>
+        <v>7.040323148520272e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>3.314979553935917e-06</v>
+        <v>3.314979553935959e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00560168916416057</v>
+        <v>0.005601689164160765</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02335356750553519</v>
+        <v>0.02335356750553523</v>
       </c>
       <c r="V9" t="n">
-        <v>2.353440918845094e-06</v>
+        <v>2.353440918845096e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.000305631555417202</v>
+        <v>0.0003056315554172028</v>
       </c>
       <c r="X9" t="n">
         <v>0.01093500427019158</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02216487253146285</v>
+        <v>0.02216487253146281</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -3232,70 +3232,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.325066600036364</v>
+        <v>-1.3250666000364</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.612434062968962</v>
+        <v>-1.612434062968964</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2213564566078986</v>
+        <v>0.2213564566078992</v>
       </c>
       <c r="G10" t="n">
-        <v>2.437057436126669e-07</v>
+        <v>2.437057436126683e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>6.401146711956965e-06</v>
+        <v>6.40114671195703e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>3.690763526468981e-05</v>
+        <v>3.690763526469016e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001591744440864191</v>
+        <v>0.0001591744440864193</v>
       </c>
       <c r="K10" t="n">
-        <v>6.232301462574491e-06</v>
+        <v>6.232301462574509e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>2.03839066761789e-06</v>
+        <v>2.038390667617891e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>2.02275367846304e-05</v>
+        <v>2.022753678463039e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001997654717969489</v>
+        <v>0.001997654717965398</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0003962917553510028</v>
+        <v>0.0003962917553510044</v>
       </c>
       <c r="P10" t="n">
-        <v>1.338598081099503e-05</v>
+        <v>1.338598081099508e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.007125988120684126</v>
+        <v>0.007125988120666061</v>
       </c>
       <c r="R10" t="n">
-        <v>6.153988721059192e-05</v>
+        <v>6.1539887210564e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.896904983858831e-06</v>
+        <v>2.896904983858827e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.003622785586672703</v>
+        <v>0.003622785586672868</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02145993041192556</v>
+        <v>0.02145993041192557</v>
       </c>
       <c r="V10" t="n">
-        <v>2.238315205429518e-06</v>
+        <v>2.238315205429519e-06</v>
       </c>
       <c r="W10" t="n">
         <v>0.0002926020834925045</v>
       </c>
       <c r="X10" t="n">
-        <v>0.010204800149993</v>
+        <v>0.01020480014999298</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02059963552342421</v>
+        <v>0.02059963552342418</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
